--- a/weekly_agent/下周潜力个股排行榜.xlsx
+++ b/weekly_agent/下周潜力个股排行榜.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>601390</t>
+          <t>600027</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -461,19 +461,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>技术面表现良好，成交量放大温和，可能为机构趋势建仓</t>
+          <t>基本面支持下的机构建仓行为推动股价上涨</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>9.97%</t>
+          <t>4.66%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>600150</t>
+          <t>600019</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -481,19 +481,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>位于MA20均线上方，成交量放大显示可能为机构建仓，短期看涨</t>
+          <t>机构趋势建仓迹象明显，短期内有望延续上涨。</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7.67%</t>
+          <t>1.48%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>302132</t>
+          <t>601618</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -501,19 +501,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>基于技术指标良好及潜在机构支持</t>
+          <t>股价已突破关键阻力位并伴随成交量放大，显示出较强的上涨动能。</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5.30%</t>
+          <t>5.20%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>601857</t>
+          <t>601669</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -521,19 +521,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>技术面良好，基本面支持，机构建仓迹象明显。</t>
+          <t>股价站稳关键均线，放量启动显示较强的资金流入意愿，基本面稳定向好</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.94%</t>
+          <t>3.84%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>600406</t>
+          <t>600584</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -541,19 +541,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>机构趋势建仓迹象明显，技术面和基本面均支持上涨</t>
+          <t>技术面强势突破，成交量健康增长，机构建仓可能性大</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.53%</t>
+          <t>9.19%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>601872</t>
+          <t>600309</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -561,39 +561,39 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>机构趋势建仓迹象明显，股价稳健</t>
+          <t>机构趋势建仓迹象明显，基本面支持较强</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>16.83%</t>
+          <t>7.28%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>601618</t>
+          <t>600018</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>机构趋势建仓迹象明显，技术面和基本面均支持上涨</t>
+          <t>机构趋势建仓迹象明显，且位于上升趋势初期</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>601669</t>
+          <t>600010</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -601,19 +601,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>股价处于MA20均线上方，成交量温和放大，基本面和技术面均支持上涨</t>
+          <t>股价处于MA20均线上方且成交量放大较为温和，更符合机构趋势建仓的特征</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>32.00%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>603296</t>
+          <t>600362</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -621,19 +621,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>股价处于MA20均线上方且有放量启动迹象，表明市场对该股兴趣浓厚</t>
+          <t>基本面和技术面均支持上涨，市场情绪积极</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6.70%</t>
+          <t>5.31%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>600026</t>
+          <t>600674</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -641,39 +641,39 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>近期股价强势突破关键阻力位，并伴有明显的资金流入迹象，预计短期内仍将维持上涨态势。</t>
+          <t>虽然存在T+1制度导致的操作限制，但鉴于当前良好的技术形态和潜在的机构参与迹象，预计下周继续上涨的概率较高。</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>17.92%</t>
+          <t>2.94%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>688009</t>
+          <t>601186</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>技术面良好，成交量温和放大，基本面支持，市场情绪稳定</t>
+          <t>良好技术形态与机构支持预期推动股价，但仍需注意短期波动风险</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.95%</t>
+          <t>1.82%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>000977</t>
+          <t>600233</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -681,19 +681,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>基于现有技术面和量价关系分析，短期存在继续上涨潜力</t>
+          <t>本周表现强劲，但需警惕短期波动风险</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3.90%</t>
+          <t>8.86%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>600023</t>
+          <t>600011</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -701,19 +701,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>股价位于MA20均线上方，成交量放大显示资金流入迹象明显，基本面若无重大变化，有望延续涨势</t>
+          <t>股价处于MA20均线上方，放量起步，技术面看涨</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2.63%</t>
+          <t>4.58%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>301269</t>
+          <t>600795</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -721,19 +721,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>技术面良好加上资金流入迹象明显，但需警惕短期波动。</t>
+          <t>股价处于上升趋势，但需警惕短期回调风险</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3.04%</t>
+          <t>6.17%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>601186</t>
+          <t>600585</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -741,19 +741,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>机构趋势建仓迹象明显，短期内具有较好的上涨潜力</t>
+          <t>基于当前的技术面和成交量情况，预计将继续保持上涨趋势</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2.10%</t>
+          <t>2.36%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>603986</t>
+          <t>601136</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -761,19 +761,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>基于当前技术面优势及潜在基本面支撑</t>
+          <t>技术面强劲且可能存在机构建仓迹象</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>10.33%</t>
+          <t>1.62%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>600089</t>
+          <t>600023</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -781,19 +781,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>股价站稳MA20均线之上，显示出较强的支持力度；同时，近期成交量温和放大暗示有新资金逐步入场。</t>
+          <t>基于当前的技术面表现良好，且存在机构建仓迹象</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2.19%</t>
+          <t>7.26%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>600027</t>
+          <t>600886</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -801,19 +801,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>近期走势稳健，成交量温和增长，显示出潜在的机构支持；同时，技术面上也处于较为有利的位置。</t>
+          <t>成交量放大配合技术面支撑，短期内维持上涨趋势可能性较大</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>600938</t>
+          <t>600183</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -821,19 +821,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>处于健康上升趋势，机构趋势建仓可能性大</t>
+          <t>机构趋势建仓迹象明显，技术面支撑较强</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>9.95%</t>
+          <t>9.77%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>601877</t>
+          <t>600930</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -841,19 +841,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>机构趋势建仓迹象明显，但需警惕短期波动</t>
+          <t>技术面良好，成交量放大，但需警惕短期回调风险</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>1.69%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>600372</t>
+          <t>600905</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -861,19 +861,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>机构趋势建仓迹象明显，技术面支持，但需警惕短期回调风险</t>
+          <t>成交量温和放大且股价站稳MA20均线之上，显示较强上行动力</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3.60%</t>
+          <t>1.47%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>000338</t>
+          <t>600089</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -881,19 +881,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>近期股价表现强劲且稳定，预计机构持续买入将支撑股价</t>
+          <t>机构趋势建仓迹象明显，短期虽有回调风险但整体向上动能较强</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>18.96%</t>
+          <t>9.86%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>601868</t>
+          <t>601600</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -901,19 +901,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>机构趋势建仓迹象明显，技术面支撑较强</t>
+          <t>技术面稳健，机构可能持续建仓</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2.55%</t>
+          <t>6.47%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>600803</t>
+          <t>600039</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -921,132 +921,112 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>机构趋势建仓迹象明显，技术面上行态势良好</t>
+          <t>机构资金持续流入，技术面支持良好</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>4.29%</t>
+          <t>1.97%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>600886</t>
+          <t>601238</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>股价稳定于关键支撑位之上，且成交量温和增加，显示出较强的持稳迹象。</t>
+          <t>尽管存在短期波动风险，但从技术面和基本面来看，该股具备一定的上升潜力。</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.54%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>600015</t>
+          <t>601117</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>股价处于MA20均线上方，平稳运行，且可能受到机构趋势建仓的影响。</t>
+          <t>处于MA20均线上方，放量起步，但需警惕冲高回落风险</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>4.61%</t>
+          <t>11.37%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>600845</t>
+          <t>600111</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>近期走势强劲且处于放量起步阶段，但需警惕短期回调风险</t>
+          <t>短期内面临获利盘抛压，但不排除继续走强可能性</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>4.54%</t>
+          <t>23.00%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>601919</t>
+          <t>600025</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>近期表现良好但缺乏基本面支持，存在短线回调风险</t>
+          <t>短期内虽显强势，但缺乏基本面支撑</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>4.38%</t>
+          <t>1.97%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>600893</t>
+          <t>600026</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>短期内涨幅较大，但缺乏基本面支撑，存在回调风险</t>
+          <t>短期内涨幅较大，可能存在游资退出风险</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>19.96%</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>600176</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>40</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>本周上涨主要由游资推动，持续性存疑，冲高回落风险较大</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>32.98%</t>
+          <t>27.23%</t>
         </is>
       </c>
     </row>
